--- a/astro-site/public/dl/catering-checklist-templates/04-catering-staff-checklists-by-role.xlsx
+++ b/astro-site/public/dl/catering-checklist-templates/04-catering-staff-checklists-by-role.xlsx
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Inventory leftovers: decide what to keep (cool it per FDA Food Code 3-501.14) and what to discard</t>
+          <t>Inventory leftovers: keep only food that stayed at 135 °F or above / 41 °F or below and never went out to guests (cool hot food from 135 °F to 70 °F within 2 h, then to 41 °F within 4 h more, FDA Food Code 3-501.14); anything that sat on the buffet or was held under time as a public health control (FDA Food Code 3-501.19) gets discarded</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -1206,7 +1206,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G27">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Handle gratuities and feedback for the service team: gratuities per house policy and your state's rules; a mandatory service charge is NOT a gratuity: for the IRS it is wages (Rev. Rul. 2012-18)</t>
+          <t>Handle gratuities and feedback for the service team: gratuities per house policy and your state's rules; managers and supervisors can't keep any part of employees' tips (FLSA); a mandatory service charge is NOT a gratuity: what you pay out of it to staff is wages for the IRS (Rev. Rul. 2012-18)</t>
         </is>
       </c>
       <c r="C26" s="19" t="inlineStr">
@@ -1742,7 +1742,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G27">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -2278,7 +2278,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G27">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Prep cocktail batches if needed (sangria, premixed gin and tonic) in their own labeled containers; never refill a liquor bottle</t>
+          <t>Prep cocktail batches if needed (sangria, punch, batched margaritas) in their own labeled containers; never refill a liquor bottle</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -2814,7 +2814,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G27">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
